--- a/public/business-plans/trade.xlsx
+++ b/public/business-plans/trade.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Торговля и общественное питание». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Торговля и общественное питание». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Кофейня «Qahva Vaqti» открывается в спальном районе Ташкента формата «кофе с собой» + 12 посадочных мест, с продажей выпечки собственного производства. Требуемые инвестиции — 480 млн сум на ремонт и оборудование; окупаемость — около 16 месяцев при среднем чеке 35 тыс. сум и 120 чеках в день.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,68 +661,84 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  Розничная торговля и общепит — один из крупнейших секторов по числу МСБ в Узбекистане.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  Розничная торговля и общепит — один из крупнейших секторов по числу МСБ в Узбекистане и одна из самых доступных точек входа для начинающего предпринимателя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт проникновение маркетплейсов (Uzum Market и др.) и сервисов доставки еды.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  E-commerce растёт стремительно: по данным Gazeta.uz, на платформе Uzum Market работает свыше 18 тыс. продавцов (рост на 32% с начала года), оборот продавцов год к году вырос на 60%, а весь GMV площадки за 2025 год превысил $500 млн (рост в 1,5 раза) при 34 млн заказов (gazeta.uz) — маркетплейсы становятся полноценным каналом сбыта, а не просто дополнением к офлайн-точке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Рост доходов населения в крупных городах повышает спрос на современный формат торговли и питания.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  90% продавцов на крупнейшем маркетплейсе — представители малого бизнеса из регионов, а не только столичные сети (gazeta.uz) — выход на маркетплейс реалистичен и для небольшого нового бизнеса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Проходимость и конкурентов в конкретной локации, средний чек по сегменту.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Конкуренты</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+          <t>•  Рост доходов населения в крупных городах повышает спрос на современный формат торговли и питания — сетевые кофейни, фудкорты, магазины у дома с удобным форматом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: в Казахстане e-commerce и маркетплейсы (Kaspi.kz) достигли большей зрелости и доли в розничном обороте — узбекский рынок ещё в фазе быстрого роста, что даёт больше пространства для новых продавцов и брендов, чем на более насыщенных соседних рынках.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Проходимость и конкурентов в конкретной локации, средний чек по сегменту — уточняйте прямым наблюдением на месте и в отраслевых обзорах ритейла.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Целевая аудитория</t>
+          <t>Конкуренты</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Целевая аудитория</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
@@ -716,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +765,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — на уровне среднего чека по району с акцентом на качество кофе и своей выпечки; продвижение — страницы в Instagram/Telegram с фото и акциями, программа лояльности (каждый 6-й кофе бесплатно), партнёрство с соседними офисами на корпоративные заказы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: закупка сырья у поставщиков → приготовление на месте → продажа в зале/навынос → учёт выручки через ККМ. Ключевые поставщики — обжарщик кофе, поставщик молочной продукции и выпечки. Требуется регистрация ККМ и санитарно-эпидемиологическое заключение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Владелец-управляющий, 2 бариста посменно, кондитер на part-time, уборщица на аутсорсе. Форма — ИП на начальном этапе, переход в ООО при расширении до сети.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Высокая конкуренция</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Уникальное позиционирование, программа лояльности</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Порча/списание товара</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Контроль запасов, принцип FIFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Изменение потребительского спроса</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Регулярный анализ продаж и ассортимента</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Высокая конкуренция в насыщенных локациях</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Уникальное позиционирование, программа лояльности, узнаваемый бренд</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Порча/списание скоропортящегося товара</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Контроль запасов, принцип FIFO, гибкое меню под остатки</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Изменение потребительского спроса и трендов</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Регулярный анализ продаж и ассортимента, тестирование новых позиций малыми партиями</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="59" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Рост комиссий и зависимость от маркетплейсов/агрегаторов доставки</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Развитие собственных каналов продаж (соцсети, повторные заказы) параллельно с маркетплейсами</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Рост арендных ставок в проходных локациях</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Долгосрочный договор аренды с фиксацией ставки, резервная локация</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Дефицит и текучесть линейного персонала (бариста, продавцы)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Понятная система мотивации, обучение при найме, комфортные условия труда</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,336 +953,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Аренда и ремонт торговой точки</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Торговое / кухонное оборудование</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Первая товарная партия / запасы</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Регистрация ККМ и разрешений</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>для общепита — санэпидзаключение</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Вывеска и брендинг</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>Регистрация продавцом на маркетплейсе</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>при онлайн-канале продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
-        <f>SUM(B7:B11)</f>
+      <c r="B13" s="16">
+        <f>SUM(B7:B12)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Розничные продажи в точке</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Онлайн-продажи / доставка</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>маркетплейсы и агрегаторы</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Опт для небольших партнёров</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Корпоративные заказы</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>для общепита — офисные обеды, кейтеринг</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>SUM(B15:B17)</f>
+      <c r="B20" s="16">
+        <f>SUM(B16:B19)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C20" s="17" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>ФОТ персонала</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Закупка товара / продуктов</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Комиссии маркетплейсов/агрегаторов доставки</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>включая кассовый учёт</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B27" s="15">
-        <f>SUM(B21:B26)</f>
+      <c r="B29" s="16">
+        <f>SUM(B23:B28)</f>
         <v/>
       </c>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Ежемесячная прибыль</t>
-        </is>
-      </c>
-      <c r="B29" s="10">
-        <f>B18-B27</f>
-        <v/>
-      </c>
+      <c r="C29" s="17" t="n"/>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ежемесячная прибыль</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>B20-B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B31" s="13">
-        <f>IFERROR(B4/B29,"—")</f>
+      <c r="B33" s="14">
+        <f>IFERROR(B4/B31,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C33" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B32" s="17">
-        <f>IFERROR(B29/B18*100,"—")</f>
+      <c r="B34" s="18">
+        <f>IFERROR(B31/B20*100,"—")</f>
         <v/>
       </c>
-      <c r="C32" s="13">
+      <c r="C34" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="35"/>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/business-plans/trade.xlsx
+++ b/public/business-plans/trade.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ТОРГОВЛЯ И ОБЩЕСТВЕННОЕ ПИТАНИЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ТОРГОВЛЯ И ОБЩЕСТВЕННОЕ ПИТАНИЕ — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Торговля и общественное питание» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Торговля и общественное питание» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B16</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,77 +563,93 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Аренда и ремонт торговой точки</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+        <v>250000000</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: отделка ~70-90 м² под кофейню (барная стойка, электрика, интерьер) в спальном районе Ташкента</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Торговое / кухонное оборудование</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+        <v>160000000</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: проф. кофемашина, кофемолки, холодильная витрина, POS-касса, мебель на 12 мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Первая товарная партия / запасы</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+        <v>45000000</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: кофе, молоко, сиропы, стаканы, ингредиенты для выпечки на первый месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Регистрация ККМ и разрешений</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>для общепита — санэпидзаключение</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+          <t>для общепита — санэпидзаключение — Пример: оценка: онлайн-касса (ККМ), санитарные и торговые разрешения</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Вывеска и брендинг</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+        <v>12000000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: наружная вывеска, дизайн меню/упаковки, форма персонала</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Регистрация продавцом на маркетплейсе</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>при онлайн-канале продаж</t>
+          <t>при онлайн-канале продаж — Пример: оценка: подключение к агрегаторам доставки (Yandex Eats, Uzum Tezkor, Wolt)</t>
         </is>
       </c>
     </row>
@@ -651,55 +675,63 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
     </row>
-    <row r="19" ht="21" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Розничные продажи в точке</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+        <v>88200000</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 70% от базовой выручки (средний чек 35 тыс. сум × 120 чеков/день × 30 дн = 126 млн сум/мес — из резюме)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Онлайн-продажи / доставка</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
+        <v>25200000</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>маркетплейсы и агрегаторы</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+          <t>маркетплейсы и агрегаторы — Пример: 20% от базовой выручки — агрегаторы доставки и соцсети/telegram-заказы</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Опт для небольших партнёров</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
+        <v>7560000</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 6% от базовой выручки — продажа выпечки/кофе небольшим офисам поблизости</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Корпоративные заказы</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0</v>
+        <v>5040000</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>для общепита — офисные обеды, кейтеринг</t>
+          <t>для общепита — офисные обеды, кейтеринг — Пример: 4% от базовой выручки — кейтеринг на офисные встречи по соседству</t>
         </is>
       </c>
     </row>
@@ -725,73 +757,93 @@
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
     </row>
-    <row r="26" ht="21" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>18000000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка аренды ~70-90 м² в спальном районе Ташкента с хорошей проходимостью</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="66" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ФОТ персонала</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>26000000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 2 бариста посменно (~4,5 млн/чел.), кондитер part-time (~3,5 млн), уборщица part-time (~2 млн); ориентир — средняя зарплата по Ташкенту 10,38 млн / по стране 6,16 млн сум (gazeta.uz, окт. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Закупка товара / продуктов</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+        <v>40300000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: COGS ≈32% от выручки — типичная доля себестоимости зерна, молока, сиропов и выпечки для кофеен to-go</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Коммунальные услуги</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <v>5000000</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: электроэнергия (кофемашина, холодильники), вода, отопление</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Комиссии маркетплейсов/агрегаторов доставки</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="21" customHeight="1">
+        <v>6300000</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~25% комиссия с выручки через доставку — типичная комиссия Yandex Eats/аналогов</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="51" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
+        <v>1700000</v>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>включая кассовый учёт</t>
+          <t>включая кассовый учёт — Пример: налог с оборота 1% для ИП/самозанятых (ставка с 2026 г., azma.uz) + фиксированный соц. налог от 1 БРВ ≈412 тыс. сум/мес</t>
         </is>
       </c>
     </row>
@@ -830,9 +882,10 @@
         <f>IFERROR(B7/B34,"—")</f>
         <v/>
       </c>
-      <c r="C36" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -845,22 +898,32 @@
         <f>IFERROR(B34/B23*100,"—")</f>
         <v/>
       </c>
-      <c r="C37" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="39" ht="50" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Сумма стартовых затрат — 480 млн сум, точно соответствует резюме. Прибыль ≈28,7 млн сум/мес даёт окупаемость ≈16,7 мес. — близко к заявленным ~16 мес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="55" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A39:C39"/>
   </mergeCells>
